--- a/docs/downloads/09/t10_sources_endettement_marovoay_bepako.xlsx
+++ b/docs/downloads/09/t10_sources_endettement_marovoay_bepako.xlsx
@@ -387,12 +387,6 @@
           <t>Autres</t>
         </is>
       </c>
-      <c r="C2">
-        <v>4</v>
-      </c>
-      <c r="D2">
-        <v>7.4</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -405,12 +399,6 @@
           <t>Commerçants</t>
         </is>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1.8</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -494,12 +482,6 @@
         <is>
           <t>Commerçants</t>
         </is>
-      </c>
-      <c r="C8">
-        <v>4</v>
-      </c>
-      <c r="D8">
-        <v>2.1</v>
       </c>
     </row>
     <row r="9">
